--- a/Lab_4/data/partB/param_optimization_process/v200_k10_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k10_s200_results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -582,25 +582,25 @@
         <v>8</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -677,46 +677,46 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -735,37 +735,37 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -787,40 +787,40 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -839,40 +839,40 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>59</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,19 +1059,19 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
         <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>56</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>50</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,25 +1215,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -1255,22 +1255,22 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14085,7 +14085,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24098,7 @@
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
